--- a/enhancements/test-files/08_Money_pc0505_2026.xlsx
+++ b/enhancements/test-files/08_Money_pc0505_2026.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,7 +534,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -510,10 +552,35 @@
         <v>46054</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45903</v>
+        <v>45885</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46053</v>
+        <v>46050</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>406.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>247.83</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P2" t="n">
+        <v>158.45</v>
       </c>
     </row>
     <row r="3">
@@ -527,7 +594,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,10 +616,35 @@
         <v>46057</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45911</v>
+        <v>45935</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>46054</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>129.79</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P3" t="n">
+        <v>57.11</v>
       </c>
     </row>
     <row r="4">
@@ -566,12 +658,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Metro Agency Group  </t>
+          <t xml:space="preserve">  Pinnacle Agency Partners  </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -588,10 +680,35 @@
         <v>46060</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45943</v>
+        <v>45825</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>779.92</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>483.55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>296.37</v>
       </c>
     </row>
     <row r="5">
@@ -623,10 +740,35 @@
         <v>46063</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45880</v>
+        <v>45913</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46063</v>
+        <v>46062</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2209.44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1259.38</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P5" t="n">
+        <v>950.0599999999999</v>
       </c>
     </row>
     <row r="6">
@@ -640,12 +782,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Apex Insurance Brokers  </t>
+          <t xml:space="preserve">  Pinnacle Agency Partners  </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -662,10 +804,35 @@
         <v>46066</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45805</v>
+        <v>45913</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46062</v>
+        <v>46065</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>237.84</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P6" t="n">
+        <v>128.07</v>
       </c>
     </row>
     <row r="7">
@@ -679,7 +846,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -701,10 +868,35 @@
         <v>46069</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45864</v>
+        <v>45920</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46065</v>
+        <v>46066</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>733.5599999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="P7" t="n">
+        <v>344.77</v>
       </c>
     </row>
     <row r="8">
@@ -718,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -736,10 +928,35 @@
         <v>46072</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45784</v>
+        <v>45802</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>979.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>636.62</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P8" t="n">
+        <v>342.79</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +975,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Brown &amp; Brown  </t>
+          <t xml:space="preserve">  Apex Insurance Brokers  </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -775,10 +992,35 @@
         <v>46075</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45957</v>
+        <v>45901</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46073</v>
+        <v>46075</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1232.67</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>554.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P9" t="n">
+        <v>677.97</v>
       </c>
     </row>
   </sheetData>
